--- a/PazarAnalizRaporu.xlsx
+++ b/PazarAnalizRaporu.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>urun_adi</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -434,102 +434,85 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>fiyat</t>
+          <t>hedef_kitle</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>talep_skoru</t>
+          <t>tahmini_maliyet_tl</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>pazarlama_metni</t>
+          <t>onerilen_satis_tl</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>trend_skoru</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KDN-001</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lidar Sensörlü Akıllı Robot Süpürge ve Mop</t>
+          <t>Kişiselleştirilebilir Oversize Tişört</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ev Teknolojileri</t>
+          <t>Giyim &amp; Moda</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14.999 TL</t>
+          <t>Gençler ve Sokak Modası Tutkunları</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Siz kahvenizi yudumlarken eviniz pırıl pırıl olsun; akıllı haritalama ile zahmetsiz temizliğin konforunu yaşayın!</t>
-        </is>
+        <v>150</v>
+      </c>
+      <c r="F2" t="n">
+        <v>450</v>
+      </c>
+      <c r="G2" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CB-001</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMOLED Ekranlı Sağlık ve Spor Takipçi Akıllı Saat</t>
+          <t>Organik Pamuklu Bebek Tulum Seti</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Giyilebilir Teknoloji</t>
+          <t>Bebek &amp; Çocuk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.499 TL</t>
+          <t>Yeni Ebeveynler</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nabzınızı, uykunuzu ve tarzınızı bileğinizde yönetin; gün boyu aktif ve bağlantıda kalın.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Çift Hazneli XXL Dijital Sıcak Hava Fritözü (Airfryer)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Küçük Ev Aletleri</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4.250 TL</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>89</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>%85 daha az yağ ile çıtır çıtır lezzetler dakikalar içinde masanızda; mutfaktaki yeni şefinizle tanışın!</t>
-        </is>
+        <v>200</v>
+      </c>
+      <c r="F3" t="n">
+        <v>590</v>
+      </c>
+      <c r="G3" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
